--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1731,6 +1731,232 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>106854525</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57255</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sjölunda, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>508506</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6537255</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-02-18</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-02-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sara Johansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sara Johansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>106566444</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57255</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sjölunda, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>508424</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6537255</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-02-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-02-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -1726,7 +1726,7 @@
         <v>106854472</v>
       </c>
       <c r="B11" t="n">
-        <v>90799</v>
+        <v>90809</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -1726,7 +1726,7 @@
         <v>106854472</v>
       </c>
       <c r="B11" t="n">
-        <v>90809</v>
+        <v>90821</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -1726,7 +1726,7 @@
         <v>106854472</v>
       </c>
       <c r="B11" t="n">
-        <v>90821</v>
+        <v>90828</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -1726,7 +1726,7 @@
         <v>106854472</v>
       </c>
       <c r="B11" t="n">
-        <v>90828</v>
+        <v>90833</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,11 +1740,6 @@
       </c>
       <c r="E11" t="n">
         <v>5442</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -1726,7 +1726,7 @@
         <v>106854472</v>
       </c>
       <c r="B11" t="n">
-        <v>90833</v>
+        <v>90846</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,6 +1740,11 @@
       </c>
       <c r="E11" t="n">
         <v>5442</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -1726,7 +1726,7 @@
         <v>106854472</v>
       </c>
       <c r="B11" t="n">
-        <v>90846</v>
+        <v>90859</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -1726,7 +1726,7 @@
         <v>106854472</v>
       </c>
       <c r="B11" t="n">
-        <v>90859</v>
+        <v>90853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -1726,7 +1726,7 @@
         <v>106854472</v>
       </c>
       <c r="B11" t="n">
-        <v>90853</v>
+        <v>90854</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -1726,7 +1726,7 @@
         <v>106854472</v>
       </c>
       <c r="B11" t="n">
-        <v>90854</v>
+        <v>90857</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1834,6 +1834,654 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128822945</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92784</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nyckelhult, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>508182</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6537409</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128836241</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92126</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nyckelhult, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>508521</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6537235</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jessica Bösel</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jessica Bösel</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128836106</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92780</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4363</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum concrescens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nyckelhult, Nrk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>508194</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6537396</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jessica Bösel</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jessica Bösel</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128822949</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92126</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nyckelhult, Nrk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>508568</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6537223</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128822950</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92126</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nyckelhult, Nrk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>508519</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6537288</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128836075</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92126</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nyckelhult, Nrk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>508512</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6537290</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jessica Bösel</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jessica Bösel</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -1839,7 +1839,7 @@
         <v>128822945</v>
       </c>
       <c r="B12" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>128836241</v>
       </c>
       <c r="B13" t="n">
-        <v>92126</v>
+        <v>92131</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>128836106</v>
       </c>
       <c r="B14" t="n">
-        <v>92780</v>
+        <v>92785</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>128822949</v>
       </c>
       <c r="B15" t="n">
-        <v>92126</v>
+        <v>92131</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>128822950</v>
       </c>
       <c r="B16" t="n">
-        <v>92126</v>
+        <v>92131</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>128836075</v>
       </c>
       <c r="B17" t="n">
-        <v>92126</v>
+        <v>92131</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -1839,7 +1839,7 @@
         <v>128822945</v>
       </c>
       <c r="B12" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>128836241</v>
       </c>
       <c r="B13" t="n">
-        <v>92131</v>
+        <v>92136</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>128836106</v>
       </c>
       <c r="B14" t="n">
-        <v>92785</v>
+        <v>92790</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>128822949</v>
       </c>
       <c r="B15" t="n">
-        <v>92131</v>
+        <v>92136</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>128822950</v>
       </c>
       <c r="B16" t="n">
-        <v>92131</v>
+        <v>92136</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>128836075</v>
       </c>
       <c r="B17" t="n">
-        <v>92131</v>
+        <v>92136</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -1836,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128822945</v>
+        <v>128836241</v>
       </c>
       <c r="B12" t="n">
-        <v>92794</v>
+        <v>92140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,46 +1847,44 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508182</v>
+        <v>508521</v>
       </c>
       <c r="R12" t="n">
-        <v>6537409</v>
+        <v>6537235</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1924,33 +1922,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128836241</v>
+        <v>128822945</v>
       </c>
       <c r="B13" t="n">
-        <v>92136</v>
+        <v>92798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,44 +1952,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508521</v>
+        <v>508182</v>
       </c>
       <c r="R13" t="n">
-        <v>6537235</v>
+        <v>6537409</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2033,19 +2029,23 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2055,7 +2055,7 @@
         <v>128836106</v>
       </c>
       <c r="B14" t="n">
-        <v>92790</v>
+        <v>92794</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>128822949</v>
       </c>
       <c r="B15" t="n">
-        <v>92136</v>
+        <v>92140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>128822950</v>
       </c>
       <c r="B16" t="n">
-        <v>92136</v>
+        <v>92140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>128836075</v>
       </c>
       <c r="B17" t="n">
-        <v>92136</v>
+        <v>92140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -1836,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128836241</v>
+        <v>128822945</v>
       </c>
       <c r="B12" t="n">
-        <v>92140</v>
+        <v>92798</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,44 +1847,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508521</v>
+        <v>508182</v>
       </c>
       <c r="R12" t="n">
-        <v>6537235</v>
+        <v>6537409</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1922,29 +1924,33 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128822945</v>
+        <v>128836241</v>
       </c>
       <c r="B13" t="n">
-        <v>92798</v>
+        <v>92140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,46 +1958,44 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508182</v>
+        <v>508521</v>
       </c>
       <c r="R13" t="n">
-        <v>6537409</v>
+        <v>6537235</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2029,23 +2033,19 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -1836,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128822945</v>
+        <v>128836241</v>
       </c>
       <c r="B12" t="n">
-        <v>92798</v>
+        <v>92140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,46 +1847,44 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508182</v>
+        <v>508521</v>
       </c>
       <c r="R12" t="n">
-        <v>6537409</v>
+        <v>6537235</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1924,33 +1922,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128836241</v>
+        <v>128822945</v>
       </c>
       <c r="B13" t="n">
-        <v>92140</v>
+        <v>92798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,44 +1952,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508521</v>
+        <v>508182</v>
       </c>
       <c r="R13" t="n">
-        <v>6537235</v>
+        <v>6537409</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2033,19 +2029,23 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -1836,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128836241</v>
+        <v>128822945</v>
       </c>
       <c r="B12" t="n">
-        <v>92140</v>
+        <v>92803</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,44 +1847,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508521</v>
+        <v>508182</v>
       </c>
       <c r="R12" t="n">
-        <v>6537235</v>
+        <v>6537409</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1922,29 +1924,33 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128822945</v>
+        <v>128836241</v>
       </c>
       <c r="B13" t="n">
-        <v>92798</v>
+        <v>92145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,46 +1958,44 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508182</v>
+        <v>508521</v>
       </c>
       <c r="R13" t="n">
-        <v>6537409</v>
+        <v>6537235</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2029,23 +2033,19 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2055,7 +2055,7 @@
         <v>128836106</v>
       </c>
       <c r="B14" t="n">
-        <v>92794</v>
+        <v>92799</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>128822949</v>
       </c>
       <c r="B15" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>128822950</v>
       </c>
       <c r="B16" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>128836075</v>
       </c>
       <c r="B17" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -1836,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128822945</v>
+        <v>128836241</v>
       </c>
       <c r="B12" t="n">
-        <v>92811</v>
+        <v>92158</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,46 +1847,44 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508182</v>
+        <v>508521</v>
       </c>
       <c r="R12" t="n">
-        <v>6537409</v>
+        <v>6537235</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1924,33 +1922,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128836241</v>
+        <v>128822945</v>
       </c>
       <c r="B13" t="n">
-        <v>92153</v>
+        <v>92816</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,44 +1952,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508521</v>
+        <v>508182</v>
       </c>
       <c r="R13" t="n">
-        <v>6537235</v>
+        <v>6537409</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2033,19 +2029,23 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2055,7 +2055,7 @@
         <v>128836106</v>
       </c>
       <c r="B14" t="n">
-        <v>92807</v>
+        <v>92812</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>128822949</v>
       </c>
       <c r="B15" t="n">
-        <v>92153</v>
+        <v>92158</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>128822950</v>
       </c>
       <c r="B16" t="n">
-        <v>92153</v>
+        <v>92158</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>128836075</v>
       </c>
       <c r="B17" t="n">
-        <v>92153</v>
+        <v>92158</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -1836,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128836241</v>
+        <v>128822945</v>
       </c>
       <c r="B12" t="n">
-        <v>92158</v>
+        <v>92819</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,44 +1847,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508521</v>
+        <v>508182</v>
       </c>
       <c r="R12" t="n">
-        <v>6537235</v>
+        <v>6537409</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1922,29 +1924,33 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128822945</v>
+        <v>128836241</v>
       </c>
       <c r="B13" t="n">
-        <v>92816</v>
+        <v>92161</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,46 +1958,44 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508182</v>
+        <v>508521</v>
       </c>
       <c r="R13" t="n">
-        <v>6537409</v>
+        <v>6537235</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2029,23 +2033,19 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2055,7 +2055,7 @@
         <v>128836106</v>
       </c>
       <c r="B14" t="n">
-        <v>92812</v>
+        <v>92815</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>128822949</v>
       </c>
       <c r="B15" t="n">
-        <v>92158</v>
+        <v>92161</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>128822950</v>
       </c>
       <c r="B16" t="n">
-        <v>92158</v>
+        <v>92161</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>128836075</v>
       </c>
       <c r="B17" t="n">
-        <v>92158</v>
+        <v>92161</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -1836,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128822945</v>
+        <v>128836241</v>
       </c>
       <c r="B12" t="n">
-        <v>92819</v>
+        <v>92161</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,46 +1847,44 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508182</v>
+        <v>508521</v>
       </c>
       <c r="R12" t="n">
-        <v>6537409</v>
+        <v>6537235</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1924,33 +1922,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128836241</v>
+        <v>128822945</v>
       </c>
       <c r="B13" t="n">
-        <v>92161</v>
+        <v>92819</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,44 +1952,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508521</v>
+        <v>508182</v>
       </c>
       <c r="R13" t="n">
-        <v>6537235</v>
+        <v>6537409</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2033,19 +2029,23 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -1836,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128836241</v>
+        <v>128822945</v>
       </c>
       <c r="B12" t="n">
-        <v>92161</v>
+        <v>92826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,44 +1847,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508521</v>
+        <v>508182</v>
       </c>
       <c r="R12" t="n">
-        <v>6537235</v>
+        <v>6537409</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1922,29 +1924,33 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128822945</v>
+        <v>128836241</v>
       </c>
       <c r="B13" t="n">
-        <v>92819</v>
+        <v>92168</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,46 +1958,44 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508182</v>
+        <v>508521</v>
       </c>
       <c r="R13" t="n">
-        <v>6537409</v>
+        <v>6537235</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2029,23 +2033,19 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2055,7 +2055,7 @@
         <v>128836106</v>
       </c>
       <c r="B14" t="n">
-        <v>92815</v>
+        <v>92822</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>128822949</v>
       </c>
       <c r="B15" t="n">
-        <v>92161</v>
+        <v>92168</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>128822950</v>
       </c>
       <c r="B16" t="n">
-        <v>92161</v>
+        <v>92168</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>128836075</v>
       </c>
       <c r="B17" t="n">
-        <v>92161</v>
+        <v>92168</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -1836,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128822945</v>
+        <v>128836241</v>
       </c>
       <c r="B12" t="n">
-        <v>92826</v>
+        <v>92175</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,46 +1847,44 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508182</v>
+        <v>508521</v>
       </c>
       <c r="R12" t="n">
-        <v>6537409</v>
+        <v>6537235</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1924,33 +1922,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128836241</v>
+        <v>128822945</v>
       </c>
       <c r="B13" t="n">
-        <v>92168</v>
+        <v>92833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,44 +1952,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508521</v>
+        <v>508182</v>
       </c>
       <c r="R13" t="n">
-        <v>6537235</v>
+        <v>6537409</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2033,19 +2029,23 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2055,7 +2055,7 @@
         <v>128836106</v>
       </c>
       <c r="B14" t="n">
-        <v>92822</v>
+        <v>92829</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>128822949</v>
       </c>
       <c r="B15" t="n">
-        <v>92168</v>
+        <v>92175</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>128822950</v>
       </c>
       <c r="B16" t="n">
-        <v>92168</v>
+        <v>92175</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>128836075</v>
       </c>
       <c r="B17" t="n">
-        <v>92168</v>
+        <v>92175</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -1836,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128836241</v>
+        <v>128822945</v>
       </c>
       <c r="B12" t="n">
-        <v>92175</v>
+        <v>92835</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,44 +1847,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508521</v>
+        <v>508182</v>
       </c>
       <c r="R12" t="n">
-        <v>6537235</v>
+        <v>6537409</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1922,29 +1924,33 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128822945</v>
+        <v>128836241</v>
       </c>
       <c r="B13" t="n">
-        <v>92833</v>
+        <v>92177</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,46 +1958,44 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508182</v>
+        <v>508521</v>
       </c>
       <c r="R13" t="n">
-        <v>6537409</v>
+        <v>6537235</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2029,23 +2033,19 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2055,7 +2055,7 @@
         <v>128836106</v>
       </c>
       <c r="B14" t="n">
-        <v>92829</v>
+        <v>92831</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>128822949</v>
       </c>
       <c r="B15" t="n">
-        <v>92175</v>
+        <v>92177</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>128822950</v>
       </c>
       <c r="B16" t="n">
-        <v>92175</v>
+        <v>92177</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>128836075</v>
       </c>
       <c r="B17" t="n">
-        <v>92175</v>
+        <v>92177</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -1836,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128822945</v>
+        <v>128836241</v>
       </c>
       <c r="B12" t="n">
-        <v>92835</v>
+        <v>92177</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,46 +1847,44 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508182</v>
+        <v>508521</v>
       </c>
       <c r="R12" t="n">
-        <v>6537409</v>
+        <v>6537235</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1924,33 +1922,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128836241</v>
+        <v>128822945</v>
       </c>
       <c r="B13" t="n">
-        <v>92177</v>
+        <v>92835</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,44 +1952,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508521</v>
+        <v>508182</v>
       </c>
       <c r="R13" t="n">
-        <v>6537235</v>
+        <v>6537409</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2033,19 +2029,23 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -1836,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128836241</v>
+        <v>128822945</v>
       </c>
       <c r="B12" t="n">
-        <v>92177</v>
+        <v>92821</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,44 +1847,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508521</v>
+        <v>508182</v>
       </c>
       <c r="R12" t="n">
-        <v>6537235</v>
+        <v>6537409</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1922,29 +1924,33 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Jessica Wiener, Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128822945</v>
+        <v>128836241</v>
       </c>
       <c r="B13" t="n">
-        <v>92835</v>
+        <v>92192</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,46 +1958,44 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>508182</v>
+        <v>508521</v>
       </c>
       <c r="R13" t="n">
-        <v>6537409</v>
+        <v>6537235</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2029,23 +2033,19 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2055,7 +2055,7 @@
         <v>128836106</v>
       </c>
       <c r="B14" t="n">
-        <v>92831</v>
+        <v>92817</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>128822949</v>
       </c>
       <c r="B15" t="n">
-        <v>92177</v>
+        <v>92192</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
+          <t>Jessica Wiener, Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2271,7 +2271,7 @@
         <v>128822950</v>
       </c>
       <c r="B16" t="n">
-        <v>92177</v>
+        <v>92192</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
+          <t>Jessica Wiener, Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2382,7 +2382,7 @@
         <v>128836075</v>
       </c>
       <c r="B17" t="n">
-        <v>92177</v>
+        <v>92192</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -1839,7 +1839,7 @@
         <v>128822945</v>
       </c>
       <c r="B12" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jessica Wiener, Emil Pagstedt Andersson</t>
+          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1950,7 +1950,7 @@
         <v>128836241</v>
       </c>
       <c r="B13" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>128836106</v>
       </c>
       <c r="B14" t="n">
-        <v>92817</v>
+        <v>92818</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>128822949</v>
       </c>
       <c r="B15" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jessica Wiener, Emil Pagstedt Andersson</t>
+          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2271,7 +2271,7 @@
         <v>128822950</v>
       </c>
       <c r="B16" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jessica Wiener, Emil Pagstedt Andersson</t>
+          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2382,7 +2382,7 @@
         <v>128836075</v>
       </c>
       <c r="B17" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106854481</v>
+        <v>106857037</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sjölunda, Nrk</t>
+          <t>Stora Hornsjön, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508485.5514368879</v>
+        <v>508230</v>
       </c>
       <c r="R2" t="n">
-        <v>6537265.570012339</v>
+        <v>6537318</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -753,19 +744,9 @@
           <t>2023-02-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-02-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,71 +761,67 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sara Johansson</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Johansson</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106854465</v>
+        <v>128836106</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>4363</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Karlslund, Nrk</t>
+          <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508477.2605061929</v>
+        <v>508194</v>
       </c>
       <c r="R3" t="n">
-        <v>6537277.925073576</v>
+        <v>6537396</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,22 +845,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-02-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-02-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,33 +859,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sara Johansson</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sara Johansson</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106854525</v>
+        <v>128822945</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,43 +889,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sjölunda, Nrk</t>
+          <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508506</v>
+        <v>508182</v>
       </c>
       <c r="R4" t="n">
-        <v>6537255</v>
+        <v>6537409</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,22 +952,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-02-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-02-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,31 +968,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sara Johansson</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sara Johansson</t>
+          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106855117</v>
+        <v>106566430</v>
       </c>
       <c r="B5" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,7 +1019,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1073,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508362.0807266876</v>
+        <v>508364</v>
       </c>
       <c r="R5" t="n">
-        <v>6537280.250572369</v>
+        <v>6537282</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1103,22 +1064,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-02-18</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:33</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-02-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:33</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,27 +1084,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sara Johansson</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sara Johansson</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106566430</v>
+        <v>106854472</v>
       </c>
       <c r="B6" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,16 +1124,7 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1195,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508363.1091917127</v>
+        <v>508488</v>
       </c>
       <c r="R6" t="n">
-        <v>6537282.315029982</v>
+        <v>6537284</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1225,22 +1162,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-02-10</t>
+          <t>2023-02-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-02-10</t>
+          <t>2023-02-18</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,27 +1192,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Git Katarina Lundström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Git Katarina Lundström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106566444</v>
+        <v>106854481</v>
       </c>
       <c r="B7" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,40 +1215,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sjölunda, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>508423</v>
+        <v>508486</v>
       </c>
       <c r="R7" t="n">
-        <v>6537255</v>
+        <v>6537266</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1343,12 +1274,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-02-10</t>
+          <t>2023-02-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-02-10</t>
+          <t>2023-02-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,27 +1304,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Sara Johansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Sara Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>106857037</v>
+        <v>106855117</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,35 +1327,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stora Hornsjön, Nrk</t>
+          <t>Karlslund, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>508229.7823517024</v>
+        <v>508362</v>
       </c>
       <c r="R8" t="n">
-        <v>6537317.600399802</v>
+        <v>6537280</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1451,7 +1391,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1401,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,63 +1416,67 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Sara Johansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Sara Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>106566359</v>
+        <v>106856567</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Karlslund, Nrk</t>
+          <t>Stora Hornsjön, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>508474.5928815522</v>
+        <v>508244</v>
       </c>
       <c r="R9" t="n">
-        <v>6537316.58566678</v>
+        <v>6537335</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1559,22 +1503,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-02-10</t>
+          <t>2023-02-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-02-10</t>
+          <t>2023-02-18</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,27 +1533,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>106856567</v>
+        <v>128822949</v>
       </c>
       <c r="B10" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,21 +1556,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1644,20 +1583,19 @@
           <t>mycel</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stora Hornsjön, Nrk</t>
+          <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>508243.6905761707</v>
+        <v>508568</v>
       </c>
       <c r="R10" t="n">
-        <v>6537334.643317943</v>
+        <v>6537223</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1681,22 +1619,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-02-18</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:57</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-02-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:57</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,70 +1635,78 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>106854472</v>
+        <v>128822950</v>
       </c>
       <c r="B11" t="n">
-        <v>90857</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>6031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Karlslund, Nrk</t>
+          <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>508488</v>
+        <v>508519</v>
       </c>
       <c r="R11" t="n">
-        <v>6537284</v>
+        <v>6537288</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1794,22 +1730,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-02-18</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-02-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,26 +1746,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Git Katarina Lundström</t>
+          <t>Emil Pagstedt Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Git Katarina Lundström</t>
+          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128822945</v>
+        <v>128836075</v>
       </c>
       <c r="B12" t="n">
-        <v>92822</v>
+        <v>92567</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,46 +1778,44 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nyckelhult, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>508182</v>
+        <v>508512</v>
       </c>
       <c r="R12" t="n">
-        <v>6537409</v>
+        <v>6537290</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1924,23 +1853,19 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
+          <t>Jessica Bösel</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1950,7 +1875,7 @@
         <v>128836241</v>
       </c>
       <c r="B13" t="n">
-        <v>92193</v>
+        <v>92567</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2052,55 +1977,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128836106</v>
+        <v>106566359</v>
       </c>
       <c r="B14" t="n">
-        <v>92818</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4363</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nyckelhult, Nrk</t>
+          <t>Karlslund, Nrk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508194</v>
+        <v>508475</v>
       </c>
       <c r="R14" t="n">
-        <v>6537396</v>
+        <v>6537317</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2124,12 +2043,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2138,29 +2057,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128822949</v>
+        <v>106566444</v>
       </c>
       <c r="B15" t="n">
-        <v>92193</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,46 +2086,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6031</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nyckelhult, Nrk</t>
+          <t>Sjölunda, Nrk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>508568</v>
+        <v>508423</v>
       </c>
       <c r="R15" t="n">
-        <v>6537223</v>
+        <v>6537255</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2231,12 +2146,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-02-10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,31 +2162,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128822950</v>
+        <v>106854465</v>
       </c>
       <c r="B16" t="n">
-        <v>92193</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2279,46 +2189,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6031</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nyckelhult, Nrk</t>
+          <t>Karlslund, Nrk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>508519</v>
+        <v>508477</v>
       </c>
       <c r="R16" t="n">
-        <v>6537288</v>
+        <v>6537278</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2342,12 +2249,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-02-18</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-02-18</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,31 +2275,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson</t>
+          <t>Sara Johansson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emil Pagstedt Andersson, Jessica Wiener</t>
+          <t>Sara Johansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128836075</v>
+        <v>106854525</v>
       </c>
       <c r="B17" t="n">
-        <v>92193</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,44 +2302,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6031</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nyckelhult, Nrk</t>
+          <t>Sjölunda, Nrk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508512</v>
+        <v>508506</v>
       </c>
       <c r="R17" t="n">
-        <v>6537290</v>
+        <v>6537255</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2451,12 +2362,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-02-18</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-02-18</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2465,22 +2386,229 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Sara Johansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jessica Bösel</t>
+          <t>Sara Johansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>106918291</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sjölunda, Nyckelhult, Nrk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>508489</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6537190</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-02-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-02-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Flög iväg ifrån trädtopp.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Rolf Wedding</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Rolf Wedding</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>106918289</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sjölunda, Nyckelhult, Nrk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>508489</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6537190</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-02-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-02-15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Rolf Wedding</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Rolf Wedding</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3674-2023 artfynd.xlsx
+++ b/artfynd/A 3674-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106857037</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128836106</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128822945</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,6 +1113,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106566430</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106854472</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,6 +1343,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106854481</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1425,6 +1460,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106855117</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1542,6 +1582,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106856567</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1653,6 +1698,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128822949</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1764,6 +1814,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128822950</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1869,6 +1924,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128836075</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1974,6 +2034,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128836241</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2072,6 +2137,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106566359</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2175,6 +2245,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106566444</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2288,6 +2363,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106854465</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2401,6 +2481,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106854525</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2507,6 +2592,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106918291</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2609,8 +2699,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106918289</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>